--- a/output/pdf_financials_xlsx/ENB.xlsx
+++ b/output/pdf_financials_xlsx/ENB.xlsx
@@ -60330,7 +60330,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -62430,7 +62430,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -63177,7 +63177,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -64564,7 +64564,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -68421,7 +68421,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -73526,7 +73526,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -85616,7 +85616,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E713" s="5" t="n">

--- a/output/pdf_financials_xlsx/ENB.xlsx
+++ b/output/pdf_financials_xlsx/ENB.xlsx
@@ -32578,7 +32578,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -55336,7 +55340,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E431" s="5" t="n">
         <v>-68</v>
       </c>

--- a/output/pdf_financials_xlsx/ENB.xlsx
+++ b/output/pdf_financials_xlsx/ENB.xlsx
@@ -1491,13 +1491,13 @@
         <v>142</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-2697</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>237</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>1708</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>774</v>
@@ -1766,20 +1766,14 @@
       <c r="K20" s="3" t="n">
         <v>2309</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L20" s="3" t="n">
+        <v>-2128</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>3807</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>9243</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>4964</v>
@@ -1981,13 +1975,13 @@
         <v>2593</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>569</v>
+        <v>-2128</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>3570</v>
+        <v>3807</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>7535</v>
+        <v>9243</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>4964</v>
@@ -2689,13 +2683,13 @@
         <v>5.793553651570788</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>473.9894551845342</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>6.638655462184874</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>22.66755142667552</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>18.47255369928401</v>
@@ -3042,34 +3036,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>907</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>1079</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
@@ -3328,28 +3320,28 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>1079</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>0</v>
@@ -3818,28 +3810,28 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2484</v>
+        <v>1803</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2706</v>
+        <v>1966</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4101</v>
+        <v>3299</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4045</v>
+        <v>3368</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5079</v>
+        <v>3925</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5792</v>
+        <v>4624</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5471</v>
+        <v>4392</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5060</v>
+        <v>4086</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>7207</v>
@@ -4416,22 +4408,22 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>29104</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>33355</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>42321</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>53974</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>64572</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>64417</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>0</v>
@@ -4486,22 +4478,22 @@
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L57" s="3" t="n">
         <v>0</v>
@@ -4992,34 +4984,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>548</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -5278,28 +5268,28 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -5768,28 +5758,28 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3789</v>
+        <v>3374</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>3355</v>
+        <v>3123</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>6165</v>
+        <v>5989</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>7069</v>
+        <v>6946</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>10728</v>
+        <v>10428</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>9501</v>
+        <v>9087</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>10814</v>
+        <v>10253</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>8243</v>
+        <v>7915</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>11753</v>
@@ -7475,13 +7465,13 @@
         <v>2593</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>569</v>
+        <v>-2128</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>3570</v>
+        <v>3807</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>7535</v>
+        <v>9243</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>4964</v>
@@ -8472,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1383</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>535</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -31364,7 +31354,11 @@
           <t>Deferred income tax expense (Note 24)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -37872,7 +37866,11 @@
           <t>Deferred income tax expense (Note 25)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -41737,7 +41735,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -52322,7 +52324,11 @@
           <t>Future income taxes (Note 26)</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -52861,7 +52867,11 @@
           <t>Proceeds on sale of investments (Note 6)</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -54591,7 +54601,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E424" s="5" t="n">
         <v>41</v>
       </c>
@@ -55879,7 +55893,11 @@
           <t>Proceeds on sale of investments (Note 6)</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -63399,7 +63417,11 @@
           <t>Income tax recovery/(expense) (Note 25)</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -64681,7 +64703,11 @@
           <t>Income tax recovery/(expense) (Note 24)</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
